--- a/Luban/DataTables/Datas/GlobalSetting.xlsx
+++ b/Luban/DataTables/Datas/GlobalSetting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26640" windowHeight="8700"/>
+    <workbookView windowWidth="26880" windowHeight="9285"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
